--- a/liste groupe 1.xlsx
+++ b/liste groupe 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1282DC74-C106-47CF-B36B-C41B565CA92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141DDDF2-7E0B-452A-9EB0-4A83CAEAE2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 1.xlsx
+++ b/liste groupe 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141DDDF2-7E0B-452A-9EB0-4A83CAEAE2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787F4706-5AA6-44DD-9136-F94B236D3CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 1.xlsx
+++ b/liste groupe 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787F4706-5AA6-44DD-9136-F94B236D3CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3BC0A2-0A0A-44EE-8C68-B89787892AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 1.xlsx
+++ b/liste groupe 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3BC0A2-0A0A-44EE-8C68-B89787892AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC32B7A-A71B-4ACE-9132-ABB737E631C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 1.xlsx
+++ b/liste groupe 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC32B7A-A71B-4ACE-9132-ABB737E631C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD0BC67-3CF0-410A-A5E3-4551038B31F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 1.xlsx
+++ b/liste groupe 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD0BC67-3CF0-410A-A5E3-4551038B31F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EA4DC7-73C2-4633-9316-698F87281FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 1.xlsx
+++ b/liste groupe 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EA4DC7-73C2-4633-9316-698F87281FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D5B41E-CEDB-462B-A061-B9BE1FB9B496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
